--- a/Evaluation/Final_Evaluation_Report.xlsx
+++ b/Evaluation/Final_Evaluation_Report.xlsx
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1.090909090909091</v>
+        <v>0.01214574898785425</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>1.090909090909091</v>
+        <v>0.01214574898785425</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>

--- a/Evaluation/Final_Evaluation_Report.xlsx
+++ b/Evaluation/Final_Evaluation_Report.xlsx
@@ -550,7 +550,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -559,19 +559,19 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.01214574898785425</v>
+        <v>0.08097165991902834</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1.404748913627679</v>
+        <v>1.406073609316836</v>
       </c>
       <c r="O2" t="n">
-        <v>1.616702853179804</v>
+        <v>1.621980537685054</v>
       </c>
       <c r="P2" t="n">
-        <v>1.510725883403742</v>
+        <v>1.514027073500945</v>
       </c>
     </row>
     <row r="3">
@@ -614,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03571428571428571</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -623,19 +623,19 @@
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01214574898785425</v>
+        <v>0.08097165991902834</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>1.404748913627679</v>
+        <v>1.406073609316836</v>
       </c>
       <c r="O3" t="n">
-        <v>1.616702853179804</v>
+        <v>1.621980537685054</v>
       </c>
       <c r="P3" t="n">
-        <v>1.510725883403742</v>
+        <v>1.514027073500945</v>
       </c>
     </row>
   </sheetData>
